--- a/test_data/gurindji_bush_medicine/data/metadata.xlsx
+++ b/test_data/gurindji_bush_medicine/data/metadata.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10315"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10322"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/abby/Documents/Work/PosterWebsites/ro-crate-html-lite/test_data/gurindji_bush_medicine/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8DEA7B64-87F3-0A4A-AF9D-DFA0C1B03780}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D673B85-D942-B84A-86FA-2850C326B2AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="17280" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="17280" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RootDataset" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="505" uniqueCount="241">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="513" uniqueCount="246">
   <si>
     <t>name</t>
   </si>
@@ -404,9 +404,6 @@
     <t>files/audio/sentences/7_partiki.mp3</t>
   </si>
   <si>
-    <t>files/audio/sentences/8_pujitilip.mp3</t>
-  </si>
-  <si>
     <t>Ocimum tenuiflorum</t>
   </si>
   <si>
@@ -437,9 +434,6 @@
     <t>Hakea arborescens</t>
   </si>
   <si>
-    <t>files/audio/names/9_ngirirri.mp3</t>
-  </si>
-  <si>
     <t>files/audio/sentences/10_karnpirrkarnpirr.mp3</t>
   </si>
   <si>
@@ -447,9 +441,6 @@
   </si>
   <si>
     <t>This is karnpirrkarnpirr. We put it on people when they have sores. On their feet, lower leg, buttocks or wherever - we treat them with this kind of plant. We grind it on a rock and then dab it on them.</t>
-  </si>
-  <si>
-    <t>Nyawa-ma karnpirrkarnpirr. Ngurnayinangulu yuwanana marntara-wu, nyamu-lu janga-ma karrwarnana. Kuyangka-ma nyarruluny-ja-ma jamana-la nyampa-ka wulu-ngka-ma maru-ngka-ma - murluny-jawung-kulu ngurnayinangulu kamparnana. Ngurnalu kutukutu yuwanana wumara-la-ma kuya. An ngurnayinangulu-rla palnyangkarra na yuwanana na.</t>
   </si>
   <si>
     <t>karnpirrkarnpirr</t>
@@ -659,12 +650,6 @@
     <t>files/audio/names/kumpulyu_VW.mp3</t>
   </si>
   <si>
-    <t>files/audio/names/wariyili_VW.mp3.mp3</t>
-  </si>
-  <si>
-    <t>files/audio/sentences/karnpirrkarnpirr_VW.mp3</t>
-  </si>
-  <si>
     <t>files/audio/names/ngirirri_VW.mp3</t>
   </si>
   <si>
@@ -683,9 +668,6 @@
     <t>files/audio/names/marlarn_VW.mp3</t>
   </si>
   <si>
-    <t>files/audio/names/4_yirrijkaji_VW.mp3</t>
-  </si>
-  <si>
     <t>files/audio/names/kupuwupu_VW.mp3</t>
   </si>
   <si>
@@ -695,9 +677,6 @@
     <t>files/images/Latest2_DSC_5138-2.JPG</t>
   </si>
   <si>
-    <t>Nicole Zicchino</t>
-  </si>
-  <si>
     <t>files/images/DSC_5102.jpg</t>
   </si>
   <si>
@@ -728,9 +707,6 @@
     <t>files/images/IMGP3029.jpeg</t>
   </si>
   <si>
-    <t>Peggy Macqueen</t>
-  </si>
-  <si>
     <t>files/images/kumpulyu.jpg</t>
   </si>
   <si>
@@ -740,12 +716,6 @@
     <t>files/images/cassie-mound.jpeg</t>
   </si>
   <si>
-    <t>Briony Barr</t>
-  </si>
-  <si>
-    <t>files/images/IMG_5358.jpg</t>
-  </si>
-  <si>
     <t>files/images/Rangers.jpg</t>
   </si>
   <si>
@@ -813,6 +783,51 @@
   </si>
   <si>
     <t>Gurindji bush medicine</t>
+  </si>
+  <si>
+    <t>files/images/parrawi.jpg</t>
+  </si>
+  <si>
+    <t>Nyawa-ma karnpirrkarnpirr. Ngurnayinangulu yuwanana marntara-wu, nyamu-lu janga-ma karrwarnana. Kuyangka-ma nyarruluny-ja-ma jamana-la nyampa-ka wulu-ngka-ma maru-ngka-ma - murluny-jawung-kulu ngurnayinangulu kamparnana. Ngurnalu kutukutu yuwanana wumara-la-ma kuya. An ngurnayinangulu-rla palyangkarra na yuwanana na palyangpalyang.</t>
+  </si>
+  <si>
+    <t>files/audio/sentences/9_ngirirri.mp3</t>
+  </si>
+  <si>
+    <t>about/speaker-headshots/ConnieNgarmeiye.jpg</t>
+  </si>
+  <si>
+    <t>about/speaker-headshots/kitty.jpg</t>
+  </si>
+  <si>
+    <t>files/audio/sentences/8_pujtilip.mp3</t>
+  </si>
+  <si>
+    <t>files/audio/names/karnpirrkarnpirr_VW.mp3</t>
+  </si>
+  <si>
+    <t>files/audio/names/wariyili_VW.mp3</t>
+  </si>
+  <si>
+    <t>files/audio/names/yirrijkaji_VW.mp3</t>
+  </si>
+  <si>
+    <t>Felicity Meakins showing Connie Ngarmeiye holding the plant</t>
+  </si>
+  <si>
+    <t>Peggy Macqueen showing Sarah Oscar holding the plant</t>
+  </si>
+  <si>
+    <t>Nicole Zicchino showing Cassandra Algy holding the plant</t>
+  </si>
+  <si>
+    <t>Nicole Zicchino showing Margaret Wynbye holding the plant</t>
+  </si>
+  <si>
+    <t>Penny Smith showing Helma Bernard and Harlem Tanami busting open partiki</t>
+  </si>
+  <si>
+    <t>Briony Barr showing Cassandra Algy holding tamarra</t>
   </si>
 </sst>
 </file>
@@ -1293,7 +1308,7 @@
         <v>0</v>
       </c>
       <c r="B4" t="s">
-        <v>239</v>
+        <v>229</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.2">
@@ -1301,7 +1316,7 @@
         <v>6</v>
       </c>
       <c r="B5" t="s">
-        <v>240</v>
+        <v>230</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.2">
@@ -1389,7 +1404,7 @@
         <v>13</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>238</v>
+        <v>228</v>
       </c>
       <c r="G1" s="2" t="s">
         <v>14</v>
@@ -1407,7 +1422,7 @@
         <v>18</v>
       </c>
       <c r="L1" s="2" t="s">
-        <v>223</v>
+        <v>213</v>
       </c>
       <c r="M1" s="2" t="s">
         <v>19</v>
@@ -1422,7 +1437,7 @@
         <v>22</v>
       </c>
       <c r="Q1" s="7" t="s">
-        <v>224</v>
+        <v>214</v>
       </c>
     </row>
     <row r="2" spans="1:17" ht="112" x14ac:dyDescent="0.2">
@@ -1458,16 +1473,16 @@
         <v>73</v>
       </c>
       <c r="L2" s="3" t="s">
-        <v>201</v>
+        <v>242</v>
       </c>
       <c r="M2" s="3" t="s">
         <v>71</v>
       </c>
       <c r="N2" s="3" t="s">
-        <v>200</v>
+        <v>194</v>
       </c>
       <c r="O2" s="3" t="s">
-        <v>199</v>
+        <v>193</v>
       </c>
       <c r="P2" s="3" t="s">
         <v>74</v>
@@ -1506,22 +1521,22 @@
         <v>77</v>
       </c>
       <c r="L3" s="3" t="s">
-        <v>201</v>
+        <v>243</v>
       </c>
       <c r="M3" s="3" t="s">
         <v>76</v>
       </c>
       <c r="N3" s="3" t="s">
-        <v>202</v>
+        <v>195</v>
       </c>
       <c r="O3" s="3" t="s">
-        <v>198</v>
+        <v>192</v>
       </c>
       <c r="P3" s="3" t="s">
         <v>75</v>
       </c>
       <c r="Q3" s="8" t="s">
-        <v>221</v>
+        <v>211</v>
       </c>
     </row>
     <row r="4" spans="1:17" ht="160" x14ac:dyDescent="0.2">
@@ -1539,7 +1554,7 @@
         <v>3</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="G4" s="3" t="s">
         <v>24</v>
@@ -1563,10 +1578,10 @@
         <v>85</v>
       </c>
       <c r="N4" s="3" t="s">
-        <v>203</v>
+        <v>196</v>
       </c>
       <c r="O4" s="3" t="s">
-        <v>196</v>
+        <v>191</v>
       </c>
       <c r="P4" s="3" t="s">
         <v>97</v>
@@ -1611,16 +1626,16 @@
         <v>86</v>
       </c>
       <c r="N5" s="3" t="s">
-        <v>204</v>
+        <v>197</v>
       </c>
       <c r="O5" s="3" t="s">
-        <v>197</v>
+        <v>239</v>
       </c>
       <c r="P5" s="3" t="s">
         <v>96</v>
       </c>
       <c r="Q5" s="8" t="s">
-        <v>221</v>
+        <v>211</v>
       </c>
     </row>
     <row r="6" spans="1:17" ht="160" x14ac:dyDescent="0.2">
@@ -1662,16 +1677,16 @@
         <v>60</v>
       </c>
       <c r="N6" s="3" t="s">
-        <v>205</v>
+        <v>198</v>
       </c>
       <c r="O6" s="3" t="s">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="P6" s="3" t="s">
         <v>95</v>
       </c>
       <c r="Q6" s="8" t="s">
-        <v>221</v>
+        <v>211</v>
       </c>
     </row>
     <row r="7" spans="1:17" ht="80" x14ac:dyDescent="0.2">
@@ -1713,10 +1728,10 @@
         <v>99</v>
       </c>
       <c r="N7" s="3" t="s">
-        <v>206</v>
+        <v>199</v>
       </c>
       <c r="O7" s="3" t="s">
-        <v>194</v>
+        <v>189</v>
       </c>
       <c r="P7" s="3" t="s">
         <v>98</v>
@@ -1755,16 +1770,16 @@
         <v>107</v>
       </c>
       <c r="L8" s="3" t="s">
-        <v>68</v>
+        <v>244</v>
       </c>
       <c r="M8" s="3" t="s">
         <v>108</v>
       </c>
       <c r="N8" s="3" t="s">
-        <v>218</v>
+        <v>208</v>
       </c>
       <c r="O8" s="3" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="P8" s="3" t="s">
         <v>109</v>
@@ -1779,7 +1794,7 @@
         <v>23</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="E9" s="3" t="s">
         <v>3</v>
@@ -1794,31 +1809,31 @@
         <v>25</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="K9" s="3" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="L9" s="3" t="s">
         <v>68</v>
       </c>
       <c r="M9" s="3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="N9" s="3" t="s">
-        <v>219</v>
+        <v>209</v>
       </c>
       <c r="O9" s="3" t="s">
-        <v>192</v>
+        <v>187</v>
       </c>
       <c r="P9" s="3" t="s">
-        <v>110</v>
+        <v>236</v>
       </c>
       <c r="Q9" s="8" t="s">
-        <v>221</v>
+        <v>211</v>
       </c>
     </row>
     <row r="10" spans="1:17" ht="160" x14ac:dyDescent="0.2">
@@ -1830,13 +1845,13 @@
         <v>23</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E10" s="3" t="s">
         <v>3</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="G10" s="3" t="s">
         <v>24</v>
@@ -1845,28 +1860,28 @@
         <v>25</v>
       </c>
       <c r="I10" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="J10" s="3" t="s">
         <v>117</v>
       </c>
-      <c r="J10" s="3" t="s">
+      <c r="K10" s="3" t="s">
         <v>118</v>
-      </c>
-      <c r="K10" s="3" t="s">
-        <v>119</v>
       </c>
       <c r="L10" s="3" t="s">
         <v>68</v>
       </c>
       <c r="M10" s="3" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="N10" s="3" t="s">
-        <v>207</v>
+        <v>200</v>
       </c>
       <c r="O10" s="3" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="P10" s="3" t="s">
-        <v>121</v>
+        <v>233</v>
       </c>
     </row>
     <row r="11" spans="1:17" ht="176" x14ac:dyDescent="0.2">
@@ -1878,7 +1893,7 @@
         <v>23</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="E11" s="3" t="s">
         <v>3</v>
@@ -1896,25 +1911,25 @@
         <v>89</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>125</v>
+        <v>232</v>
       </c>
       <c r="K11" s="3" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="L11" s="3" t="s">
-        <v>212</v>
+        <v>241</v>
       </c>
       <c r="M11" s="3" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="N11" s="3" t="s">
-        <v>211</v>
+        <v>204</v>
       </c>
       <c r="O11" s="3" t="s">
-        <v>190</v>
+        <v>237</v>
       </c>
       <c r="P11" s="3" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
     </row>
     <row r="12" spans="1:17" ht="144" x14ac:dyDescent="0.2">
@@ -1926,7 +1941,7 @@
         <v>23</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="E12" s="3" t="s">
         <v>3</v>
@@ -1944,25 +1959,25 @@
         <v>89</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="K12" s="3" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="L12" s="3" t="s">
-        <v>210</v>
+        <v>240</v>
       </c>
       <c r="M12" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="N12" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="O12" s="3" t="s">
+        <v>238</v>
+      </c>
+      <c r="P12" s="3" t="s">
         <v>128</v>
-      </c>
-      <c r="N12" s="3" t="s">
-        <v>208</v>
-      </c>
-      <c r="O12" s="3" t="s">
-        <v>189</v>
-      </c>
-      <c r="P12" s="3" t="s">
-        <v>131</v>
       </c>
     </row>
     <row r="13" spans="1:17" ht="176" x14ac:dyDescent="0.2">
@@ -1974,7 +1989,7 @@
         <v>23</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="E13" s="3" t="s">
         <v>3</v>
@@ -1989,31 +2004,31 @@
         <v>25</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="K13" s="3" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="L13" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="M13" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="N13" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="O13" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="P13" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="Q13" s="8" t="s">
         <v>210</v>
-      </c>
-      <c r="M13" s="3" t="s">
-        <v>132</v>
-      </c>
-      <c r="N13" s="3" t="s">
-        <v>213</v>
-      </c>
-      <c r="O13" s="3" t="s">
-        <v>188</v>
-      </c>
-      <c r="P13" s="3" t="s">
-        <v>174</v>
-      </c>
-      <c r="Q13" s="8" t="s">
-        <v>220</v>
       </c>
     </row>
     <row r="14" spans="1:17" ht="160" x14ac:dyDescent="0.2">
@@ -2025,7 +2040,7 @@
         <v>23</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>3</v>
@@ -2040,28 +2055,28 @@
         <v>25</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="K14" s="3" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="L14" s="3" t="s">
         <v>68</v>
       </c>
       <c r="M14" s="3" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="N14" s="3" t="s">
-        <v>214</v>
+        <v>206</v>
       </c>
       <c r="O14" s="3" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="P14" s="3" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
     </row>
     <row r="15" spans="1:17" ht="256" x14ac:dyDescent="0.2">
@@ -2073,7 +2088,7 @@
         <v>23</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="E15" s="3" t="s">
         <v>3</v>
@@ -2088,31 +2103,31 @@
         <v>25</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="K15" s="3" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="L15" s="3" t="s">
-        <v>216</v>
+        <v>245</v>
       </c>
       <c r="M15" s="3" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="N15" s="3" t="s">
-        <v>215</v>
+        <v>207</v>
       </c>
       <c r="O15" s="3" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="P15" s="3" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="Q15" s="8" t="s">
-        <v>222</v>
+        <v>212</v>
       </c>
     </row>
     <row r="16" spans="1:17" ht="144" x14ac:dyDescent="0.2">
@@ -2124,7 +2139,7 @@
         <v>23</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="E16" s="3" t="s">
         <v>3</v>
@@ -2139,28 +2154,28 @@
         <v>25</v>
       </c>
       <c r="I16" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="J16" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="K16" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="L16" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="M16" s="3" t="s">
         <v>149</v>
       </c>
-      <c r="J16" s="3" t="s">
-        <v>150</v>
-      </c>
-      <c r="K16" s="3" t="s">
-        <v>151</v>
-      </c>
-      <c r="L16" s="3" t="s">
-        <v>210</v>
-      </c>
-      <c r="M16" s="3" t="s">
-        <v>152</v>
-      </c>
       <c r="N16" s="3" t="s">
-        <v>209</v>
+        <v>202</v>
       </c>
       <c r="O16" s="3" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="P16" s="3" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
     </row>
     <row r="17" spans="1:16" ht="96" x14ac:dyDescent="0.2">
@@ -2172,7 +2187,7 @@
         <v>23</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="E17" s="3" t="s">
         <v>3</v>
@@ -2187,28 +2202,28 @@
         <v>25</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="K17" s="3" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="L17" s="3" t="s">
         <v>68</v>
       </c>
       <c r="M17" s="3" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="N17" s="3" t="s">
-        <v>217</v>
+        <v>231</v>
       </c>
       <c r="O17" s="3" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="P17" s="3" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
     </row>
   </sheetData>
@@ -2248,24 +2263,24 @@
     </row>
     <row r="2" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A2" s="3" t="s">
-        <v>200</v>
+        <v>194</v>
       </c>
       <c r="B2" t="s">
         <v>27</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A3" s="3" t="s">
-        <v>199</v>
+        <v>193</v>
       </c>
       <c r="B3" t="s">
         <v>27</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="16" x14ac:dyDescent="0.2">
@@ -2276,29 +2291,29 @@
         <v>27</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A5" s="3" t="s">
-        <v>202</v>
+        <v>195</v>
       </c>
       <c r="B5" t="s">
         <v>27</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A6" s="3" t="s">
-        <v>198</v>
+        <v>192</v>
       </c>
       <c r="B6" t="s">
         <v>27</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="16" x14ac:dyDescent="0.2">
@@ -2309,29 +2324,29 @@
         <v>27</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A8" s="3" t="s">
-        <v>203</v>
+        <v>196</v>
       </c>
       <c r="B8" t="s">
         <v>27</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A9" s="3" t="s">
-        <v>196</v>
+        <v>191</v>
       </c>
       <c r="B9" t="s">
         <v>27</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="16" x14ac:dyDescent="0.2">
@@ -2342,29 +2357,29 @@
         <v>27</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A11" s="3" t="s">
-        <v>204</v>
+        <v>197</v>
       </c>
       <c r="B11" t="s">
         <v>27</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A12" s="3" t="s">
-        <v>197</v>
+        <v>239</v>
       </c>
       <c r="B12" t="s">
         <v>27</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="16" x14ac:dyDescent="0.2">
@@ -2375,29 +2390,29 @@
         <v>27</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A14" s="3" t="s">
-        <v>205</v>
+        <v>198</v>
       </c>
       <c r="B14" t="s">
         <v>27</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
     </row>
     <row r="15" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A15" s="3" t="s">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="B15" t="s">
         <v>27</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
     </row>
     <row r="16" spans="1:4" ht="16" x14ac:dyDescent="0.2">
@@ -2408,29 +2423,29 @@
         <v>27</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
     </row>
     <row r="17" spans="1:3" ht="16" x14ac:dyDescent="0.2">
       <c r="A17" s="3" t="s">
-        <v>206</v>
+        <v>199</v>
       </c>
       <c r="B17" t="s">
         <v>27</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
     </row>
     <row r="18" spans="1:3" ht="16" x14ac:dyDescent="0.2">
       <c r="A18" s="3" t="s">
-        <v>194</v>
+        <v>189</v>
       </c>
       <c r="B18" t="s">
         <v>27</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
     </row>
     <row r="19" spans="1:3" ht="16" x14ac:dyDescent="0.2">
@@ -2441,29 +2456,29 @@
         <v>27</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
     </row>
     <row r="20" spans="1:3" ht="16" x14ac:dyDescent="0.2">
       <c r="A20" s="3" t="s">
-        <v>218</v>
+        <v>208</v>
       </c>
       <c r="B20" t="s">
         <v>27</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
     </row>
     <row r="21" spans="1:3" ht="16" x14ac:dyDescent="0.2">
       <c r="A21" s="3" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="B21" t="s">
         <v>27</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
     </row>
     <row r="22" spans="1:3" ht="16" x14ac:dyDescent="0.2">
@@ -2474,309 +2489,309 @@
         <v>27</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
     </row>
     <row r="23" spans="1:3" ht="16" x14ac:dyDescent="0.2">
       <c r="A23" s="3" t="s">
-        <v>219</v>
+        <v>209</v>
       </c>
       <c r="B23" t="s">
         <v>27</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
     </row>
     <row r="24" spans="1:3" ht="16" x14ac:dyDescent="0.2">
       <c r="A24" s="3" t="s">
-        <v>192</v>
+        <v>187</v>
       </c>
       <c r="B24" t="s">
         <v>27</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
     </row>
     <row r="25" spans="1:3" ht="16" x14ac:dyDescent="0.2">
       <c r="A25" s="3" t="s">
-        <v>110</v>
+        <v>236</v>
       </c>
       <c r="B25" t="s">
         <v>27</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
     </row>
     <row r="26" spans="1:3" ht="16" x14ac:dyDescent="0.2">
       <c r="A26" s="3" t="s">
-        <v>207</v>
+        <v>200</v>
       </c>
       <c r="B26" t="s">
         <v>27</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
     </row>
     <row r="27" spans="1:3" ht="16" x14ac:dyDescent="0.2">
       <c r="A27" s="3" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="B27" t="s">
         <v>27</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
     </row>
     <row r="28" spans="1:3" ht="16" x14ac:dyDescent="0.2">
       <c r="A28" s="3" t="s">
-        <v>121</v>
+        <v>233</v>
       </c>
       <c r="B28" t="s">
         <v>27</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
     </row>
     <row r="29" spans="1:3" ht="16" x14ac:dyDescent="0.2">
       <c r="A29" s="3" t="s">
-        <v>211</v>
+        <v>204</v>
       </c>
       <c r="B29" t="s">
         <v>27</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
     </row>
     <row r="30" spans="1:3" ht="16" x14ac:dyDescent="0.2">
       <c r="A30" s="3" t="s">
-        <v>190</v>
+        <v>237</v>
       </c>
       <c r="B30" t="s">
         <v>27</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
     </row>
     <row r="31" spans="1:3" ht="16" x14ac:dyDescent="0.2">
       <c r="A31" s="3" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="B31" t="s">
         <v>27</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
     </row>
     <row r="32" spans="1:3" ht="16" x14ac:dyDescent="0.2">
       <c r="A32" s="3" t="s">
-        <v>208</v>
+        <v>201</v>
       </c>
       <c r="B32" t="s">
         <v>27</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
     </row>
     <row r="33" spans="1:3" ht="16" x14ac:dyDescent="0.2">
       <c r="A33" s="3" t="s">
-        <v>189</v>
+        <v>238</v>
       </c>
       <c r="B33" t="s">
         <v>27</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
     </row>
     <row r="34" spans="1:3" ht="16" x14ac:dyDescent="0.2">
       <c r="A34" s="3" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="B34" t="s">
         <v>27</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
     </row>
     <row r="35" spans="1:3" ht="16" x14ac:dyDescent="0.2">
       <c r="A35" s="3" t="s">
-        <v>213</v>
+        <v>205</v>
       </c>
       <c r="B35" t="s">
         <v>27</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
     </row>
     <row r="36" spans="1:3" ht="16" x14ac:dyDescent="0.2">
       <c r="A36" s="3" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="B36" t="s">
         <v>27</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
     </row>
     <row r="37" spans="1:3" ht="16" x14ac:dyDescent="0.2">
       <c r="A37" s="3" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="B37" t="s">
         <v>27</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
     </row>
     <row r="38" spans="1:3" ht="16" x14ac:dyDescent="0.2">
       <c r="A38" s="3" t="s">
-        <v>214</v>
+        <v>206</v>
       </c>
       <c r="B38" t="s">
         <v>27</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
     </row>
     <row r="39" spans="1:3" ht="16" x14ac:dyDescent="0.2">
       <c r="A39" s="3" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="B39" t="s">
         <v>27</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
     </row>
     <row r="40" spans="1:3" ht="16" x14ac:dyDescent="0.2">
       <c r="A40" s="3" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="B40" t="s">
         <v>27</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
     </row>
     <row r="41" spans="1:3" ht="16" x14ac:dyDescent="0.2">
       <c r="A41" s="3" t="s">
-        <v>215</v>
+        <v>207</v>
       </c>
       <c r="B41" t="s">
         <v>27</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
     </row>
     <row r="42" spans="1:3" ht="16" x14ac:dyDescent="0.2">
       <c r="A42" s="3" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="B42" t="s">
         <v>27</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
     </row>
     <row r="43" spans="1:3" ht="16" x14ac:dyDescent="0.2">
       <c r="A43" s="3" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="B43" t="s">
         <v>27</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
     </row>
     <row r="44" spans="1:3" ht="16" x14ac:dyDescent="0.2">
       <c r="A44" s="3" t="s">
-        <v>209</v>
+        <v>202</v>
       </c>
       <c r="B44" t="s">
         <v>27</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
     </row>
     <row r="45" spans="1:3" ht="16" x14ac:dyDescent="0.2">
       <c r="A45" s="3" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="B45" t="s">
         <v>27</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
     </row>
     <row r="46" spans="1:3" ht="16" x14ac:dyDescent="0.2">
       <c r="A46" s="3" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="B46" t="s">
         <v>27</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
     </row>
     <row r="47" spans="1:3" ht="16" x14ac:dyDescent="0.2">
       <c r="A47" s="3" t="s">
-        <v>217</v>
+        <v>231</v>
       </c>
       <c r="B47" t="s">
         <v>27</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
     </row>
     <row r="48" spans="1:3" ht="16" x14ac:dyDescent="0.2">
       <c r="A48" s="3" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B48" t="s">
         <v>27</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
     </row>
     <row r="49" spans="1:3" ht="16" x14ac:dyDescent="0.2">
       <c r="A49" s="3" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="B49" t="s">
         <v>27</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
     </row>
     <row r="50" spans="1:3" ht="16" x14ac:dyDescent="0.2">
       <c r="A50" s="9" t="s">
-        <v>235</v>
+        <v>225</v>
       </c>
       <c r="B50" s="9" t="s">
         <v>27</v>
@@ -2787,7 +2802,7 @@
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A51" s="9" t="s">
-        <v>236</v>
+        <v>226</v>
       </c>
       <c r="B51" s="9" t="s">
         <v>27</v>
@@ -2798,7 +2813,7 @@
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A52" s="9" t="s">
-        <v>237</v>
+        <v>227</v>
       </c>
       <c r="B52" s="9" t="s">
         <v>27</v>
@@ -2807,9 +2822,27 @@
         <v>65</v>
       </c>
     </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A53" s="9" t="s">
+        <v>234</v>
+      </c>
+      <c r="B53" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="C53" t="s">
+        <v>175</v>
+      </c>
+    </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A54" s="3"/>
-      <c r="C54" s="3"/>
+      <c r="A54" s="9" t="s">
+        <v>235</v>
+      </c>
+      <c r="B54" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="C54" t="s">
+        <v>178</v>
+      </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A55" s="3"/>
@@ -3046,26 +3079,28 @@
         <v>61</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>234</v>
+        <v>224</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>235</v>
+        <v>225</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="B3" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="D3" s="9" t="s">
+        <v>224</v>
+      </c>
+      <c r="E3" s="9" t="s">
         <v>234</v>
       </c>
-      <c r="E3" s="9"/>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
@@ -3078,10 +3113,10 @@
         <v>64</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>234</v>
+        <v>224</v>
       </c>
       <c r="E4" s="9" t="s">
-        <v>236</v>
+        <v>226</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.2">
@@ -3095,24 +3130,27 @@
         <v>67</v>
       </c>
       <c r="D5" s="9" t="s">
-        <v>234</v>
+        <v>224</v>
       </c>
       <c r="E5" s="9" t="s">
-        <v>237</v>
+        <v>227</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="B6" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="C6" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="D6" s="9" t="s">
-        <v>234</v>
+        <v>224</v>
+      </c>
+      <c r="E6" s="9" t="s">
+        <v>235</v>
       </c>
     </row>
   </sheetData>
@@ -3259,44 +3297,44 @@
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A10" s="9" t="s">
-        <v>225</v>
+        <v>215</v>
       </c>
       <c r="B10" s="9" t="s">
         <v>29</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>226</v>
+        <v>216</v>
       </c>
       <c r="D10" s="9" t="s">
-        <v>227</v>
+        <v>217</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A11" s="9" t="s">
-        <v>228</v>
+        <v>218</v>
       </c>
       <c r="B11" s="9" t="s">
         <v>29</v>
       </c>
       <c r="C11" s="9" t="s">
-        <v>229</v>
+        <v>219</v>
       </c>
       <c r="D11" s="9" t="s">
-        <v>230</v>
+        <v>220</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A12" s="9" t="s">
-        <v>231</v>
+        <v>221</v>
       </c>
       <c r="B12" s="9" t="s">
         <v>29</v>
       </c>
       <c r="C12" s="9" t="s">
-        <v>232</v>
+        <v>222</v>
       </c>
       <c r="D12" s="9" t="s">
-        <v>233</v>
+        <v>223</v>
       </c>
     </row>
   </sheetData>
